--- a/BD.xlsx
+++ b/BD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1450" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{905D745C-1A0F-41F1-9BAF-788845677FCF}"/>
+  <xr:revisionPtr revIDLastSave="1474" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9BE935-15BB-4405-8F73-6D1E2443AF90}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-1" sheetId="14" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="322">
   <si>
     <t>Proyecto</t>
   </si>
@@ -973,6 +973,39 @@
   </si>
   <si>
     <t>CHATA ICACSA</t>
+  </si>
+  <si>
+    <t>A.S/0056-126</t>
+  </si>
+  <si>
+    <t>A.S/0056</t>
+  </si>
+  <si>
+    <t>A.S/0059</t>
+  </si>
+  <si>
+    <t>EP MODESTO 6</t>
+  </si>
+  <si>
+    <t>A.S/0059-126</t>
+  </si>
+  <si>
+    <t>EP TIBURON 5 (EX TASA 31)</t>
+  </si>
+  <si>
+    <t>A.S/0057</t>
+  </si>
+  <si>
+    <t>A.S/0057-126</t>
+  </si>
+  <si>
+    <t>GP/90-225</t>
+  </si>
+  <si>
+    <t>GP/90</t>
+  </si>
+  <si>
+    <t>TASA 111 (DESGUACE)</t>
   </si>
 </sst>
 </file>
@@ -1557,13 +1590,55 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C9" s="1"/>
+      <c r="A9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C10" s="1"/>
+      <c r="A10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C11" s="1"/>
+      <c r="A11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>317</v>
+      </c>
+      <c r="E11" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
@@ -3609,7 +3684,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A90B3A0-EF1B-440D-B3D5-8495F9519A3D}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.21875" customWidth="1"/>
@@ -3723,6 +3798,23 @@
         <v>253</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E7" t="s">
+        <v>319</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1474" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9BE935-15BB-4405-8F73-6D1E2443AF90}"/>
+  <xr:revisionPtr revIDLastSave="1484" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973E1D45-F99C-4222-AE85-7086EA2CAE11}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-1" sheetId="14" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="2023-2" sheetId="11" r:id="rId6"/>
     <sheet name="Modulo" sheetId="13" r:id="rId7"/>
     <sheet name="desguace" sheetId="12" r:id="rId8"/>
+    <sheet name="Construccion" sheetId="15" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="326">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1006,6 +1007,18 @@
   </si>
   <si>
     <t>TASA 111 (DESGUACE)</t>
+  </si>
+  <si>
+    <t>AS/73-122</t>
+  </si>
+  <si>
+    <t>AS/73</t>
+  </si>
+  <si>
+    <t>E/P MODESTO 8</t>
+  </si>
+  <si>
+    <t>Construccion</t>
   </si>
 </sst>
 </file>
@@ -3819,4 +3832,54 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD85E68-4BF5-480F-890C-483ABC2B1F16}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BD.xlsx
+++ b/BD.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1484" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973E1D45-F99C-4222-AE85-7086EA2CAE11}"/>
+  <xr:revisionPtr revIDLastSave="1494" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{406C08E3-F947-491F-8E86-E44BEBB4EB93}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="1104" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-1" sheetId="14" r:id="rId1"/>
-    <sheet name="2025-2" sheetId="10" r:id="rId2"/>
-    <sheet name="2025-1" sheetId="9" r:id="rId3"/>
-    <sheet name="2024-2" sheetId="8" r:id="rId4"/>
-    <sheet name="2024-1" sheetId="6" r:id="rId5"/>
-    <sheet name="2023-2" sheetId="11" r:id="rId6"/>
-    <sheet name="Modulo" sheetId="13" r:id="rId7"/>
-    <sheet name="desguace" sheetId="12" r:id="rId8"/>
-    <sheet name="Construccion" sheetId="15" r:id="rId9"/>
+    <sheet name="2026-2" sheetId="16" r:id="rId1"/>
+    <sheet name="2026-1" sheetId="14" r:id="rId2"/>
+    <sheet name="2025-2" sheetId="10" r:id="rId3"/>
+    <sheet name="2025-1" sheetId="9" r:id="rId4"/>
+    <sheet name="2024-2" sheetId="8" r:id="rId5"/>
+    <sheet name="2024-1" sheetId="6" r:id="rId6"/>
+    <sheet name="2023-2" sheetId="11" r:id="rId7"/>
+    <sheet name="Modulo" sheetId="13" r:id="rId8"/>
+    <sheet name="desguace" sheetId="12" r:id="rId9"/>
+    <sheet name="Construccion" sheetId="15" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="330">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1019,6 +1020,18 @@
   </si>
   <si>
     <t>Construccion</t>
+  </si>
+  <si>
+    <t>GO/52</t>
+  </si>
+  <si>
+    <t>GO/53</t>
+  </si>
+  <si>
+    <t>GO/52-226</t>
+  </si>
+  <si>
+    <t>GO/53-226</t>
   </si>
 </sst>
 </file>
@@ -1451,6 +1464,152 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406CE352-F3DC-4CF5-AA00-B0ED30D6C318}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD85E68-4BF5-480F-890C-483ABC2B1F16}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603E48AC-9EDB-4CF6-8126-8AFAD8689F3B}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1683,7 +1842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C3AA09-1F79-4F4D-BB06-15A57FFB3161}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2026,7 +2185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2EAE93-250F-45C5-8452-04778CDF69D5}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2401,7 +2560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F31B70A-7AC0-4170-8EDB-19BFB91944E2}">
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3088,7 +3247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE99D356-A7AD-4D03-BA66-90BB63C41FBC}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3513,7 +3672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66D469D-263F-4468-BBFB-44CB0C55D551}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3585,7 +3744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36C664E-B6C5-4289-80E5-BE01E283E5BC}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3695,7 +3854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A90B3A0-EF1B-440D-B3D5-8495F9519A3D}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3832,54 +3991,4 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD85E68-4BF5-480F-890C-483ABC2B1F16}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/BD.xlsx
+++ b/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1494" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{406C08E3-F947-491F-8E86-E44BEBB4EB93}"/>
+  <xr:revisionPtr revIDLastSave="1498" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE1CFF3-B3CC-419F-B415-E1F0185A20F9}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="1104" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27000" yWindow="1440" windowWidth="27000" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-2" sheetId="16" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="332">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1032,6 +1032,12 @@
   </si>
   <si>
     <t>GO/53-226</t>
+  </si>
+  <si>
+    <t>CHATA TAMAKUN</t>
+  </si>
+  <si>
+    <t>2026-2</t>
   </si>
 </sst>
 </file>
@@ -1498,10 +1504,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="B2" t="s">
-        <v>290</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>155</v>
@@ -1515,10 +1521,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="B3" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>155</v>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1498" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE1CFF3-B3CC-419F-B415-E1F0185A20F9}"/>
+  <xr:revisionPtr revIDLastSave="1504" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67EB0499-B6B3-4789-95C5-ED9718149E19}"/>
   <bookViews>
-    <workbookView xWindow="-27000" yWindow="1440" windowWidth="27000" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-2" sheetId="16" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="335">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1038,6 +1038,15 @@
   </si>
   <si>
     <t>2026-2</t>
+  </si>
+  <si>
+    <t>A.S/0060-126</t>
+  </si>
+  <si>
+    <t>A.S/0060</t>
+  </si>
+  <si>
+    <t>LANCHA ACUARIO</t>
   </si>
 </sst>
 </file>
@@ -1819,7 +1828,21 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C12" s="1"/>
+      <c r="A12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" t="s">
+        <v>334</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1504" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67EB0499-B6B3-4789-95C5-ED9718149E19}"/>
+  <xr:revisionPtr revIDLastSave="1511" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0DAAA8-9D67-42C7-B49E-ED486B266479}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-2" sheetId="16" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="338">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1047,6 +1047,15 @@
   </si>
   <si>
     <t>LANCHA ACUARIO</t>
+  </si>
+  <si>
+    <t>A.S/0061-226</t>
+  </si>
+  <si>
+    <t>A.S/0061</t>
+  </si>
+  <si>
+    <t>EP PDA 2</t>
   </si>
 </sst>
 </file>
@@ -1546,7 +1555,21 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C4" s="1"/>
+      <c r="A4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" t="s">
+        <v>336</v>
+      </c>
+      <c r="E4" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1511" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0DAAA8-9D67-42C7-B49E-ED486B266479}"/>
+  <xr:revisionPtr revIDLastSave="1534" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6852A2A-C9F8-4CCD-857D-5663476B1376}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="349">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1056,6 +1056,39 @@
   </si>
   <si>
     <t>EP PDA 2</t>
+  </si>
+  <si>
+    <t>EP BRUNELLA II</t>
+  </si>
+  <si>
+    <t>A.S/0064</t>
+  </si>
+  <si>
+    <t>A.S/0064-226</t>
+  </si>
+  <si>
+    <t>A.S/0063</t>
+  </si>
+  <si>
+    <t>A.S/0063-226</t>
+  </si>
+  <si>
+    <t>Remolcador de bahía</t>
+  </si>
+  <si>
+    <t>FA/20</t>
+  </si>
+  <si>
+    <t>FA/20-226</t>
+  </si>
+  <si>
+    <t>A.S/0062</t>
+  </si>
+  <si>
+    <t>A.S/0062-226</t>
+  </si>
+  <si>
+    <t>REM VICHAMA</t>
   </si>
 </sst>
 </file>
@@ -1572,16 +1605,72 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C5" s="1"/>
+      <c r="A5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E5" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C6" s="1"/>
+      <c r="A6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E6" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C7" s="1"/>
+      <c r="A7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E7" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C8" s="1"/>
+      <c r="A8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E8" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tasaomega-my.sharepoint.com/personal/barevalo_tasa_com_pe1/Documents/Balois -2024/GITHUB CP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barevalo\OneDrive - Tecnológica de Alimentos S.A\Balois -2024\GITHUB CP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1534" documentId="11_BB3868379BEBDFD1702DBB10282470997ACE9E53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6852A2A-C9F8-4CCD-857D-5663476B1376}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34CBA43-F557-4DB6-BA1B-498EE36F12E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="352">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1089,6 +1089,15 @@
   </si>
   <si>
     <t>REM VICHAMA</t>
+  </si>
+  <si>
+    <t>A.S/0065</t>
+  </si>
+  <si>
+    <t>A.S/0065-226</t>
+  </si>
+  <si>
+    <t>EP SIMY 3</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1682,21 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C9" s="1"/>
+      <c r="A9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
